--- a/WorkBot/refactor-experimental/data/orders/Webstaurant/Webstaurant_Bakery_20251109.xlsx
+++ b/WorkBot/refactor-experimental/data/orders/Webstaurant/Webstaurant_Bakery_20251109.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -551,6 +551,114 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>102708283KT</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Spice - Ginger (Ground)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>72.99</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>72.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>10201311</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Spice - Italian Seasoning</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>87.89</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>87.89</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>10200013</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Herb - Basil (Dried)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>32.49</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>32.49</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>245885CB</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Box Cake - 8x8x5</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>34.81</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>69.62</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/WorkBot/refactor-experimental/data/orders/Webstaurant/Webstaurant_Bakery_20251109.xlsx
+++ b/WorkBot/refactor-experimental/data/orders/Webstaurant/Webstaurant_Bakery_20251109.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -659,6 +659,195 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>500CTOUT160</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Java Box (160oz)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>95.99</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>287.97</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>5000TOUT96</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Java Box (96oz)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>82.99</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>331.96</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2458GCC</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Cake Circle - 8" (Gold)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>39.49</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>78.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>245CCGR2518</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Cake Board - Full Sheet</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>56.99</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>113.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>245882WB</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Box Cake - 8x8x2.5 (window)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>68.60</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>137.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>150BB4224N</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Bag Paper - Baguette</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>118.99</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>237.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>656095131</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Container - Muffin (12 Pack)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>56.49</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>56.49</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/WorkBot/refactor-experimental/data/orders/Webstaurant/Webstaurant_Bakery_20251109.xlsx
+++ b/WorkBot/refactor-experimental/data/orders/Webstaurant/Webstaurant_Bakery_20251109.xlsx
@@ -446,120 +446,120 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>8808604CS</t>
+          <t>8808607CS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Torani - White Chocolate Sauce</t>
+          <t>Torani - Pumpkin Pie Sauce</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>72.69</t>
+          <t>71.49</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>145.38</t>
+          <t>71.49</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>8808607CS</t>
+          <t>8808605CS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Torani - Pumpkin Pie Sauce</t>
+          <t>Torani - Dark Chocolate Sauce</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>71.49</t>
+          <t>67.89</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>71.49</t>
+          <t>678.90</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>8808605CS</t>
+          <t>8808606CS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Torani - Dark Chocolate Sauce</t>
+          <t>Torani - Caramel Sauce</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>67.89</t>
+          <t>72.69</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>678.90</t>
+          <t>218.07</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>8808606CS</t>
+          <t>102708283KT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Torani - Caramel Sauce</t>
+          <t>Spice - Ginger (Ground)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>72.69</t>
+          <t>72.99</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>218.07</t>
+          <t>72.99</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>102708283KT</t>
+          <t>10201311</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Spice - Ginger (Ground)</t>
+          <t>Spice - Italian Seasoning</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -569,24 +569,24 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>72.99</t>
+          <t>87.89</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>72.99</t>
+          <t>87.89</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10201311</t>
+          <t>10200013</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Spice - Italian Seasoning</t>
+          <t>Herb - Basil (Dried)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -596,132 +596,132 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>87.89</t>
+          <t>32.49</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>87.89</t>
+          <t>32.49</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10200013</t>
+          <t>245885CB</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Herb - Basil (Dried)</t>
+          <t>Box Cake - 8x8x5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>32.49</t>
+          <t>34.81</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>32.49</t>
+          <t>69.62</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>245885CB</t>
+          <t>500CTOUT160</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Box Cake - 8x8x5</t>
+          <t>Java Box (160oz)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>34.81</t>
+          <t>95.99</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>69.62</t>
+          <t>287.97</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>500CTOUT160</t>
+          <t>5000TOUT96</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Java Box (160oz)</t>
+          <t>Java Box (96oz)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>95.99</t>
+          <t>82.99</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>287.97</t>
+          <t>331.96</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>5000TOUT96</t>
+          <t>2458GCC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Java Box (96oz)</t>
+          <t>Cake Circle - 8" (Gold)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>82.99</t>
+          <t>39.49</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>331.96</t>
+          <t>78.98</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2458GCC</t>
+          <t>245CCGR2518</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Cake Circle - 8" (Gold)</t>
+          <t>Cake Board - Full Sheet</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -731,24 +731,24 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>39.49</t>
+          <t>56.99</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>78.98</t>
+          <t>113.98</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>245CCGR2518</t>
+          <t>245882WB</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Cake Board - Full Sheet</t>
+          <t>Box Cake - 8x8x2.5 (window)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -758,24 +758,24 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>56.99</t>
+          <t>68.60</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>113.98</t>
+          <t>137.20</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>245882WB</t>
+          <t>150BB4224N</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Box Cake - 8x8x2.5 (window)</t>
+          <t>Bag Paper - Baguette</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -785,66 +785,66 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>68.60</t>
+          <t>118.99</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>137.20</t>
+          <t>237.98</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>150BB4224N</t>
+          <t>656095131</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Bag Paper - Baguette</t>
+          <t>Container - Muffin (12 Pack)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>118.99</t>
+          <t>56.49</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>237.98</t>
+          <t>56.49</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>656095131</t>
+          <t>110TWNG09KT3</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Container - Muffin (12 Pack)</t>
+          <t>Tea Bags - Earl Grey (Twinings)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>56.49</t>
+          <t>20.49</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>56.49</t>
+          <t>204.90</t>
         </is>
       </c>
     </row>

--- a/WorkBot/refactor-experimental/data/orders/Webstaurant/Webstaurant_Bakery_20251109.xlsx
+++ b/WorkBot/refactor-experimental/data/orders/Webstaurant/Webstaurant_Bakery_20251109.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,20 +454,14 @@
           <t>Torani - Pumpkin Pie Sauce</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>71.49</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>71.49</t>
-        </is>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>71.48999999999999</v>
+      </c>
+      <c r="E2" t="n">
+        <v>71.48999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -481,20 +475,14 @@
           <t>Torani - Dark Chocolate Sauce</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>67.89</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>678.90</t>
-        </is>
+      <c r="C3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D3" t="n">
+        <v>67.89</v>
+      </c>
+      <c r="E3" t="n">
+        <v>678.9</v>
       </c>
     </row>
     <row r="4">
@@ -508,20 +496,14 @@
           <t>Torani - Caramel Sauce</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>72.69</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>218.07</t>
-        </is>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>72.69</v>
+      </c>
+      <c r="E4" t="n">
+        <v>218.07</v>
       </c>
     </row>
     <row r="5">
@@ -535,20 +517,14 @@
           <t>Spice - Ginger (Ground)</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>72.99</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>72.99</t>
-        </is>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>72.98999999999999</v>
+      </c>
+      <c r="E5" t="n">
+        <v>72.98999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -562,20 +538,14 @@
           <t>Spice - Italian Seasoning</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>87.89</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>87.89</t>
-        </is>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>87.89</v>
+      </c>
+      <c r="E6" t="n">
+        <v>87.89</v>
       </c>
     </row>
     <row r="7">
@@ -589,20 +559,14 @@
           <t>Herb - Basil (Dried)</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>32.49</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>32.49</t>
-        </is>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>32.49</v>
+      </c>
+      <c r="E7" t="n">
+        <v>32.49</v>
       </c>
     </row>
     <row r="8">
@@ -616,20 +580,14 @@
           <t>Box Cake - 8x8x5</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>34.81</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>69.62</t>
-        </is>
+      <c r="C8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" t="n">
+        <v>34.81</v>
+      </c>
+      <c r="E8" t="n">
+        <v>69.62</v>
       </c>
     </row>
     <row r="9">
@@ -643,20 +601,14 @@
           <t>Java Box (160oz)</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>95.99</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>287.97</t>
-        </is>
+      <c r="C9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" t="n">
+        <v>95.98999999999999</v>
+      </c>
+      <c r="E9" t="n">
+        <v>287.97</v>
       </c>
     </row>
     <row r="10">
@@ -670,20 +622,14 @@
           <t>Java Box (96oz)</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>82.99</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>331.96</t>
-        </is>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>82.98999999999999</v>
+      </c>
+      <c r="E10" t="n">
+        <v>331.96</v>
       </c>
     </row>
     <row r="11">
@@ -697,20 +643,14 @@
           <t>Cake Circle - 8" (Gold)</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>39.49</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>78.98</t>
-        </is>
+      <c r="C11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" t="n">
+        <v>39.49</v>
+      </c>
+      <c r="E11" t="n">
+        <v>78.98</v>
       </c>
     </row>
     <row r="12">
@@ -724,20 +664,14 @@
           <t>Cake Board - Full Sheet</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>56.99</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>113.98</t>
-        </is>
+      <c r="C12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" t="n">
+        <v>56.99</v>
+      </c>
+      <c r="E12" t="n">
+        <v>113.98</v>
       </c>
     </row>
     <row r="13">
@@ -751,20 +685,14 @@
           <t>Box Cake - 8x8x2.5 (window)</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>68.60</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>137.20</t>
-        </is>
+      <c r="C13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" t="n">
+        <v>68.59999999999999</v>
+      </c>
+      <c r="E13" t="n">
+        <v>137.2</v>
       </c>
     </row>
     <row r="14">
@@ -778,20 +706,14 @@
           <t>Bag Paper - Baguette</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>118.99</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>237.98</t>
-        </is>
+      <c r="C14" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" t="n">
+        <v>118.99</v>
+      </c>
+      <c r="E14" t="n">
+        <v>237.98</v>
       </c>
     </row>
     <row r="15">
@@ -805,20 +727,14 @@
           <t>Container - Muffin (12 Pack)</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>56.49</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>56.49</t>
-        </is>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="n">
+        <v>56.49</v>
+      </c>
+      <c r="E15" t="n">
+        <v>56.49</v>
       </c>
     </row>
     <row r="16">
@@ -832,20 +748,56 @@
           <t>Tea Bags - Earl Grey (Twinings)</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>20.49</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>204.90</t>
-        </is>
+      <c r="C16" t="n">
+        <v>10</v>
+      </c>
+      <c r="D16" t="n">
+        <v>20.49</v>
+      </c>
+      <c r="E16" t="n">
+        <v>204.9</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>40862029</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>White Hot Chocolate - Ghirardelli</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" t="n">
+        <v>53.39</v>
+      </c>
+      <c r="E17" t="n">
+        <v>106.78</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>104ADWHEYPRO</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Supplement - Whey Protein</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" t="n">
+        <v>52.83</v>
+      </c>
+      <c r="E18" t="n">
+        <v>52.83</v>
       </c>
     </row>
   </sheetData>

--- a/WorkBot/refactor-experimental/data/orders/Webstaurant/Webstaurant_Bakery_20251109.xlsx
+++ b/WorkBot/refactor-experimental/data/orders/Webstaurant/Webstaurant_Bakery_20251109.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -800,6 +800,174 @@
         <v>52.83</v>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>3639225435</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Compound - Mocha</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="n">
+        <v>69.98999999999999</v>
+      </c>
+      <c r="E19" t="n">
+        <v>69.98999999999999</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>3639225768</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Compound - Raspberry</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="n">
+        <v>72.48999999999999</v>
+      </c>
+      <c r="E20" t="n">
+        <v>72.48999999999999</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>10207579</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Salt - Sea Coarse</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>4</v>
+      </c>
+      <c r="D21" t="n">
+        <v>21.17</v>
+      </c>
+      <c r="E21" t="n">
+        <v>84.68000000000001</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>711RGRMCRK50</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Graham Cracker - Crumb</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" t="n">
+        <v>116.44</v>
+      </c>
+      <c r="E22" t="n">
+        <v>232.88</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>335AJ330810</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Panini Sheets - 16x8 3/8</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>4</v>
+      </c>
+      <c r="D23" t="n">
+        <v>41.49</v>
+      </c>
+      <c r="E23" t="n">
+        <v>165.96</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>77031906</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Loaf Pan - Large Rectangle (paper)</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" t="n">
+        <v>134.08</v>
+      </c>
+      <c r="E24" t="n">
+        <v>268.16</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>150300865</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Bag Paper - 6x13.5 Window</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>3</v>
+      </c>
+      <c r="D25" t="n">
+        <v>79.98999999999999</v>
+      </c>
+      <c r="E25" t="n">
+        <v>239.97</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>433qlinerbl</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Sheet Pan Liner - White</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>5</v>
+      </c>
+      <c r="D26" t="n">
+        <v>46.99</v>
+      </c>
+      <c r="E26" t="n">
+        <v>234.95</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
